--- a/PSCBOX_BUKSIL_DIAPHRAGM_P1.xlsx
+++ b/PSCBOX_BUKSIL_DIAPHRAGM_P1.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J132"/>
+  <dimension ref="A1:N204"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3103,26 +3103,763 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t># ================= REBAR — 다음 단계 =================</t>
+          <t># ================= REBAR ================================================</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>#  면 철근망 : srebar code 1 (곧은 철근 열차 — 자리에서 태어나 양쪽으로 자라다 처음 만나는 피복선에서 멈춘다)</t>
+          <t># 아래 「rebar」 「crebar」 두 덩어리는 S15 (bench/fixture/s15.json) 의 철근 행을 **그대로** 옮긴 것이다 (2026-10-18).</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>#  개구부    : 개구부 면은 피복면(인력장)이다 — 철근망은 거기서 멈추므로 저절로 잘린다 · M1~M3 는 그 면에 앉는다</t>
+          <t>#   S15 는 같은 도면(8-244)에서 만든 옛 엔진용 입력이다 — 데크 철근은 벽 id(set)로 앉힌다.</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
+        <is>
+          <t>#   ! J 엔진을 격벽 페이지에 붙일 때 이 데크 철근은 init 방식으로 다시 적어야 한다 (양평대교 시트처럼).</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>#     set 기반 옛 입력은 J 엔진의 계약이 아니다 (STATUS : S15 1-1[b] 피복이 J 에서 −109.5).</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>#   crebar ⑩ 은 교축방향 닫힌 고리(3D)라 2D 검증에는 안 쓰지만, 페이지가 3D 로 세우므로 그대로 둔다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t># ---- rebar : 상부슬래브 + 좌우 캔틸레버 H13 (주두부 배근도(2) / 8-244) ----</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t># trebar | id | code | dia | init x,y,rot | set | segs | angs | nors | end:start | end:end | radius | z</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>#   code 1 = 직선(A) · 11 = ㄱ자(A→B). angs 의 a 는 A 다음 꺾임각이다</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>#   set 은 벽 id — E1/E2 데크 상면, E12·E13 좌측 캔틸레버 하면, E5·E4 우측 캔틸레버 하면</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>#   꺾임각 88.282 / 91.718 은 데크 -3% 경사에 대해 다리가 연직이라는 뜻이다 (90 ∓ 1.718)</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>#   세그먼트는 도면 그림 순서대로 — 자유단(190 다리)에서 안쪽으로</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>#   N=33 은 교축방향 개수(세그먼트 18,000 에 ctc 약 550)라 이 블록에는 안 들어간다</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>trebar</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="C143" t="n">
+        <v>11</v>
+      </c>
+      <c r="D143" t="n">
+        <v>13</v>
+      </c>
+      <c r="E143" t="inlineStr"/>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>b:E1</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>a:190,b:4800</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>a:88.282</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr"/>
+      <c r="J143" t="inlineStr"/>
+      <c r="K143" t="inlineStr"/>
+      <c r="L143" t="inlineStr"/>
+      <c r="M143" t="n">
+        <v>0</v>
+      </c>
+      <c r="N143" t="inlineStr">
+        <is>
+          <t>deck top, left  · 190 leg at the left tip + 4,500 + 300 lap = 4,990</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>trebar</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C144" t="n">
+        <v>11</v>
+      </c>
+      <c r="D144" t="n">
+        <v>13</v>
+      </c>
+      <c r="E144" t="inlineStr"/>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>a:E2</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>a:7810,b:190</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>a:91.718</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr"/>
+      <c r="J144" t="inlineStr"/>
+      <c r="K144" t="inlineStr"/>
+      <c r="L144" t="inlineStr"/>
+      <c r="M144" t="n">
+        <v>0</v>
+      </c>
+      <c r="N144" t="inlineStr">
+        <is>
+          <t>deck top, right · 300 lap + 7,510 + 190 leg at the right tip = 8,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t># trebar</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="C145" t="n">
+        <v>11</v>
+      </c>
+      <c r="D145" t="n">
+        <v>13</v>
+      </c>
+      <c r="E145" t="inlineStr"/>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>b:E13</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>a:190,b:1400</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>a:-91.718</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr"/>
+      <c r="J145" t="inlineStr"/>
+      <c r="K145" t="inlineStr"/>
+      <c r="L145" t="inlineStr"/>
+      <c r="M145" t="n">
+        <v>0</v>
+      </c>
+      <c r="N145" t="inlineStr">
+        <is>
+          <t>off for now: the left wall runs the other way, so tip+inward is not reachable. Restore once the engine can grow against the wall direction</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>trebar</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C146" t="n">
+        <v>11</v>
+      </c>
+      <c r="D146" t="n">
+        <v>13</v>
+      </c>
+      <c r="E146" t="inlineStr"/>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>b:E4</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>a:190,b:1400</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>a:88.282</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr"/>
+      <c r="J146" t="inlineStr"/>
+      <c r="K146" t="inlineStr"/>
+      <c r="L146" t="inlineStr"/>
+      <c r="M146" t="n">
+        <v>0</v>
+      </c>
+      <c r="N146" t="inlineStr">
+        <is>
+          <t>right cantilever soffit at the tip = 1,590 (leg first — stands at the tip, x=6,154)</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>trebar</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>4-1</t>
+        </is>
+      </c>
+      <c r="C147" t="n">
+        <v>1</v>
+      </c>
+      <c r="D147" t="n">
+        <v>13</v>
+      </c>
+      <c r="E147" t="inlineStr"/>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>a:E12</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>a:2540</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr"/>
+      <c r="I147" t="inlineStr"/>
+      <c r="J147" t="inlineStr"/>
+      <c r="K147" t="inlineStr"/>
+      <c r="L147" t="inlineStr"/>
+      <c r="M147" t="n">
+        <v>0</v>
+      </c>
+      <c r="N147" t="inlineStr">
+        <is>
+          <t>left  cantilever soffit, straight</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>trebar</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>3-1</t>
+        </is>
+      </c>
+      <c r="C148" t="n">
+        <v>1</v>
+      </c>
+      <c r="D148" t="n">
+        <v>13</v>
+      </c>
+      <c r="E148" t="inlineStr"/>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>a:E5</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>a:2730</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr"/>
+      <c r="I148" t="inlineStr"/>
+      <c r="J148" t="inlineStr"/>
+      <c r="K148" t="inlineStr"/>
+      <c r="L148" t="inlineStr"/>
+      <c r="M148" t="n">
+        <v>0</v>
+      </c>
+      <c r="N148" t="inlineStr">
+        <is>
+          <t>right cantilever soffit, straight</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t># ---- crebar : 격벽 폐합철근 ⑩ ⑩-1 ⑩-2 (교축방향 · 닫힌 고리) ----</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t># 다른 철근(trebar)은 단면 평면에 눕는다. 이 셋은 그 평면과 90° 다르다 —</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>#   격벽의 두께(교축 z)를 감아 도는 닫힌 고리다. 단면도에서는 선 하나로만 보인다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t># 놓는 방법 : 높이 y 에서 격벽을 수평으로 자르면 평면이 하나 나온다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>#   그 평면의 콘크리트는 「그 높이의 단면 폭 x 격벽 두께」인 직사각형이고,</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>#   고리는 그 네 면을 피복만큼 띄우고 감는다. 세그먼트가 벽을 찾아가는 것은</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>#   지금 trebar 와 똑같다 — 평면만 90° 돌아간 것이다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>#   그래서 폭을 적지 않는다. 높이만 주면 폭은 콘크리트가 정한다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t># crebar | id | dia | plane | at | set | lap | from | to | ctc</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>#   plane yz = 위치 x=at 에서 세로로 자른다 → 고리의 긴 축이 수직 (도면의 ⑩ ⑩-1 ⑩-2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>#   plane xz = 높이 y=at 에서 수평으로 자른다 → 긴 축이 가로</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>#   at : cell 복부 사이(기본) · all 단면 전체 · -6000~6000 범위 · -1100 한 자리</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t># 폭은 입력이 아니지만, 도면의 랩 포함 길이와 맞는지 보는 눈금은 된다 :</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>#   둘레 = 2 x (폭 + 두께) , 두께 2,000 일 때</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>#     ⑩   11,624 → 폭  3,812      ⑩-1  12,624 → 폭  4,312</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>#     ⑩-2 27,124 → 폭 11,562</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>#   셋 다 두께 2,000 에서 정수로 떨어진다 — 격벽 두께 2,000 의 뒷받침이다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>#   놓고 나서 나온 폭이 이 값과 맞으면 높이 at 이 맞은 것이다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>!</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>! 페이지가 이 블록을 읽는다 — 높이 at 에서 격벽을 수평으로 자른 평면에 U자(21)를</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>!   안착시킨 뒤 마지막 한 변을 이어 닫는다. 3D 에 보라색으로 선다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>! 지금 돌린 결과 : ⑩ 6,893 · ⑩-1 6,893 · ⑩-2 10,747 (감은 폭, 두께 1,901)</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>!   ⑩ ⑩-1 이 기대폭(3,812 / 4,312)과 안 맞는다 — 그 높이의 단면 폭이 7,000 이라</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>! 시험해 본 결과 (tools/plan_hoop_test.js — 엔진을 그대로 돌린 것) :</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>!   · 교축방향 평면 자체는 문제가 없다. 물리는 2D 평면 하나만 알 뿐 그것이</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>!     단면인지 수평면인지 모른다. 이 평면에 직선(code 1) · ㄱ자(11) · U자(21) 를</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>!     떨어뜨리면 전부 안착하고, 벽에서 52 = 피복 40 + 지름반 12.5 로 정확히 선다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>!   · U자(21)를 두께를 감는 크기로 주면 앞뒤 두 면과 옆면을 함께 문다</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>!     (z −948 ~ 953, 벽은 ∓1,000) — 이것이 곧 「고리에서 한 변만 빠진 것」이다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>!   · 막히는 것은 닫힘 하나뿐이다. code 41(다섯 조각)은 치수를 어떻게 주든,</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>!     set 을 주든 안 주든 ASSEMBLING 에서 멈춘다. 엔진에 닫힌 형상이 없다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>!   → 그러므로 폐합철근은 U자(21) + 닫는 한 변으로 세우는 길이 열려 있다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>!   단면 전체를 감으면 6,893 이 될 수밖에 없다. 이 둘은 단면 전체가 아니라</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>!   더 좁은 무엇(복부 한 쪽·개구부 둘레 등)을 감는 고리로 보인다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>!   ⑩-2 는 10,747 로 기대 11,562 에 815 모자라다 — at 을 데크 쪽으로 올리면 맞는다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>crebar</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="C188" t="n">
+        <v>25</v>
+      </c>
+      <c r="D188" t="inlineStr"/>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>cell</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr"/>
+      <c r="G188" t="n">
+        <v>300</v>
+      </c>
+      <c r="H188" t="inlineStr"/>
+      <c r="I188" t="inlineStr"/>
+      <c r="J188" t="n">
+        <v>150</v>
+      </c>
+      <c r="K188" t="inlineStr">
+        <is>
+          <t>hoop 10 — between the webs, 150 ctc, evenly spread. Where it crosses the opening it splits by itself into 10-1 / 10-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t># ---- 다음에 넣을 것 : 면 철근망 · 개구부 보강 (srebar code 1 — 페이지 지원을 만든 뒤) ----</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>#   지금 페이지는 srebar 를 건너뛴다. 읽을 수 없는 줄을 미리 적어 두지 않는다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>#   8-244 벡터로 잰 자리 (녹색 선, 단면 좌표 · 상면 중심선 = 0) :</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>#     M1 H25 L=2,000 N=84  세로 : x = ±726 · ±825 · ±924 (한쪽 3 개 · 약 100 간격 · 첫 줄이 개구부 옆면에서 126)</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>#                          y −6,555 ~ −4,557 (개구부 가운데 높이에 가운데)</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>#     M2 H25 L=2,000 N=84  가로(−3% 기울기, 개구부 위아래 면과 나란) : 위 3 · 아래 3 · 약 100 간격</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>#                          가운데선에서 위 y ≈ −4,700 · −4,600 · −4,500 / 아래 y ≈ −6,400 · −6,500 · −6,600</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>#     M3 H25 L=1,500 N=168 사선 45° : 모서리 접기 넷에 3 개씩 · 약 100 간격</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>#   ! 「한 면에 나란한 철근 3 개를 100 간격으로」는 trebar 로 못 적는다 — 각자 면에 앉아 서로 붙어 쌓인다(25 간격).</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>#     그래서 철근망과 같은 srebar code 1 (곧은 철근 열차)로 넣는다 : 열차 간격 ctc 100 · 길이는 고정(L).</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>#   면 철근망 : 세로(⑩ ⑪ 고리의 세로 다리 · ⑬) · 가로(⑫ ⑭) 대부분 150 간격 — 자리에서 태어나 양쪽으로 자라다</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>#     처음 만나는 피복선(외곽 · 개구부 · 덕트)에서 멈춘다. 개구부에서 저절로 잘린다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>#   도면 치수 (세로 철근 x, 왼쪽 복부 바깥에서) : 153 · 150 · 175 · 3@150 · 118 · 150 · 132 · 190 · 150 · 210 · 10@150 · 122 (중심선)</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>#   도면 치수 (가로 철근 y, 위에서) : 97.5 · 26@150 = 3,900 · 113 · 187 · 18@150 = 2,700 · 125 · 77.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
         <is>
           <t>end</t>
         </is>

--- a/PSCBOX_BUKSIL_DIAPHRAGM_P1.xlsx
+++ b/PSCBOX_BUKSIL_DIAPHRAGM_P1.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N204"/>
+  <dimension ref="A1:N214"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1232,7 +1232,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>#   clr 25 는 S14 와 같다 (도면에 순간격 표기 없음).</t>
+          <t>#   clr 0 (2026-10-18 · 사용자 결정 (가)) — 도면이 철근을 덕트에 붙여 그렸다 : 8-244 실측 순간격 −2.3 · 0.2 · 0.2 · 4.0 · 5.3 mm. 처음 넣었던 25(S14 값)로는 도면 배치가 안 나온다</t>
         </is>
       </c>
     </row>
@@ -1274,7 +1274,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="73">
@@ -1308,7 +1308,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">
@@ -1342,7 +1342,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="75">
@@ -1376,7 +1376,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76">
@@ -1410,7 +1410,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="77">
@@ -1444,7 +1444,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="78">
@@ -1478,7 +1478,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="79">
@@ -1512,7 +1512,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="80">
@@ -1546,7 +1546,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="81">
@@ -1580,7 +1580,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="82">
@@ -1614,7 +1614,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83">
@@ -1648,7 +1648,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="84">
@@ -1682,7 +1682,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="85">
@@ -1716,7 +1716,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="86">
@@ -1750,7 +1750,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="87">
@@ -1784,7 +1784,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="88">
@@ -1818,7 +1818,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89">
@@ -1852,7 +1852,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="90">
@@ -1886,7 +1886,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="91">
@@ -1920,7 +1920,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="92">
@@ -1954,7 +1954,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="93">
@@ -1988,7 +1988,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="94">
@@ -2022,7 +2022,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="95">
@@ -2056,7 +2056,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="96">
@@ -2090,7 +2090,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="97">
@@ -2124,7 +2124,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="98">
@@ -2158,7 +2158,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="99">
@@ -2192,7 +2192,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="100">
@@ -2226,7 +2226,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="101">
@@ -2260,7 +2260,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="102">
@@ -2294,7 +2294,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="103">
@@ -2328,7 +2328,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="104">
@@ -2362,7 +2362,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="105">
@@ -2396,7 +2396,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="106">
@@ -2437,7 +2437,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="108">
@@ -2471,7 +2471,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="109">
@@ -2505,7 +2505,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="110">
@@ -2539,7 +2539,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="111">
@@ -2573,7 +2573,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="112">
@@ -2607,7 +2607,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="113">
@@ -2641,7 +2641,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="114">
@@ -2675,7 +2675,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="115">
@@ -2709,7 +2709,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="116">
@@ -2743,7 +2743,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="117">
@@ -2777,7 +2777,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="118">
@@ -2811,7 +2811,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="119">
@@ -2852,7 +2852,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="121">
@@ -2886,7 +2886,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="122">
@@ -2920,7 +2920,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="123">
@@ -2954,7 +2954,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="124">
@@ -2988,7 +2988,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="125">
@@ -3022,7 +3022,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="126">
@@ -3056,7 +3056,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="127">
@@ -3090,7 +3090,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="128">
@@ -3142,6 +3142,7 @@
         </is>
       </c>
     </row>
+    <row r="135"/>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
@@ -3208,7 +3209,6 @@
       <c r="D143" t="n">
         <v>13</v>
       </c>
-      <c r="E143" t="inlineStr"/>
       <c r="F143" t="inlineStr">
         <is>
           <t>b:E1</t>
@@ -3224,10 +3224,6 @@
           <t>a:88.282</t>
         </is>
       </c>
-      <c r="I143" t="inlineStr"/>
-      <c r="J143" t="inlineStr"/>
-      <c r="K143" t="inlineStr"/>
-      <c r="L143" t="inlineStr"/>
       <c r="M143" t="n">
         <v>0</v>
       </c>
@@ -3254,7 +3250,6 @@
       <c r="D144" t="n">
         <v>13</v>
       </c>
-      <c r="E144" t="inlineStr"/>
       <c r="F144" t="inlineStr">
         <is>
           <t>a:E2</t>
@@ -3270,10 +3265,6 @@
           <t>a:91.718</t>
         </is>
       </c>
-      <c r="I144" t="inlineStr"/>
-      <c r="J144" t="inlineStr"/>
-      <c r="K144" t="inlineStr"/>
-      <c r="L144" t="inlineStr"/>
       <c r="M144" t="n">
         <v>0</v>
       </c>
@@ -3300,7 +3291,6 @@
       <c r="D145" t="n">
         <v>13</v>
       </c>
-      <c r="E145" t="inlineStr"/>
       <c r="F145" t="inlineStr">
         <is>
           <t>b:E13</t>
@@ -3316,10 +3306,6 @@
           <t>a:-91.718</t>
         </is>
       </c>
-      <c r="I145" t="inlineStr"/>
-      <c r="J145" t="inlineStr"/>
-      <c r="K145" t="inlineStr"/>
-      <c r="L145" t="inlineStr"/>
       <c r="M145" t="n">
         <v>0</v>
       </c>
@@ -3346,7 +3332,6 @@
       <c r="D146" t="n">
         <v>13</v>
       </c>
-      <c r="E146" t="inlineStr"/>
       <c r="F146" t="inlineStr">
         <is>
           <t>b:E4</t>
@@ -3362,10 +3347,6 @@
           <t>a:88.282</t>
         </is>
       </c>
-      <c r="I146" t="inlineStr"/>
-      <c r="J146" t="inlineStr"/>
-      <c r="K146" t="inlineStr"/>
-      <c r="L146" t="inlineStr"/>
       <c r="M146" t="n">
         <v>0</v>
       </c>
@@ -3392,7 +3373,6 @@
       <c r="D147" t="n">
         <v>13</v>
       </c>
-      <c r="E147" t="inlineStr"/>
       <c r="F147" t="inlineStr">
         <is>
           <t>a:E12</t>
@@ -3403,11 +3383,6 @@
           <t>a:2540</t>
         </is>
       </c>
-      <c r="H147" t="inlineStr"/>
-      <c r="I147" t="inlineStr"/>
-      <c r="J147" t="inlineStr"/>
-      <c r="K147" t="inlineStr"/>
-      <c r="L147" t="inlineStr"/>
       <c r="M147" t="n">
         <v>0</v>
       </c>
@@ -3434,7 +3409,6 @@
       <c r="D148" t="n">
         <v>13</v>
       </c>
-      <c r="E148" t="inlineStr"/>
       <c r="F148" t="inlineStr">
         <is>
           <t>a:E5</t>
@@ -3445,11 +3419,6 @@
           <t>a:2730</t>
         </is>
       </c>
-      <c r="H148" t="inlineStr"/>
-      <c r="I148" t="inlineStr"/>
-      <c r="J148" t="inlineStr"/>
-      <c r="K148" t="inlineStr"/>
-      <c r="L148" t="inlineStr"/>
       <c r="M148" t="n">
         <v>0</v>
       </c>
@@ -3459,6 +3428,7 @@
         </is>
       </c>
     </row>
+    <row r="149"/>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
@@ -3739,18 +3709,14 @@
       <c r="C188" t="n">
         <v>25</v>
       </c>
-      <c r="D188" t="inlineStr"/>
       <c r="E188" t="inlineStr">
         <is>
           <t>cell</t>
         </is>
       </c>
-      <c r="F188" t="inlineStr"/>
       <c r="G188" t="n">
         <v>300</v>
       </c>
-      <c r="H188" t="inlineStr"/>
-      <c r="I188" t="inlineStr"/>
       <c r="J188" t="n">
         <v>150</v>
       </c>
@@ -3760,17 +3726,18 @@
         </is>
       </c>
     </row>
+    <row r="189"/>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t># ---- 다음에 넣을 것 : 면 철근망 · 개구부 보강 (srebar code 1 — 페이지 지원을 만든 뒤) ----</t>
+          <t># ---- 다음에 넣을 것 : 가로 철근망 · 개구부 보강 (srebar code 1) — 세로 철근망은 맨 아래에 넣었다 ----</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>#   지금 페이지는 srebar 를 건너뛴다. 읽을 수 없는 줄을 미리 적어 두지 않는다.</t>
+          <t>#   격벽 페이지가 srebar code 1 을 읽는다 (2026-10-18). 갈고리(21 · 21a)는 아직 건너뛴다.</t>
         </is>
       </c>
     </row>
@@ -3860,6 +3827,130 @@
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t># ---- srebar code 1 : 세로 면 철근망 — 덕트가 먼저 밀고, 개구부가 나중에 자른다 (2026-10-18) ----</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t># srebar | id | code | dia | init x,y,rot | range | num | ctc | | | | | z</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>#   rot 90 = 세로 철근. 열차는 +x 로 행진하고 init 이 열차의 한가운데다. 철근 길이는 입력이 아니다 — 그 직선 위의 콘크리트가 낸다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>#   자리 : 중심선에서 ±(122 + 150k), k = 0…21 (도면의 가운데 122 · 10@150) → 한쪽 22 개, init x = ∓(122 + 150 × 10.5) = ∓1,697</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>#   ① 외곽만 본 철근을 덕트가 제 칸(±75) 안에서 옆으로 민다  ② 밀린 자리에서 개구부가 자른다 (위 · 아래 두 토막)</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>#   ! 복부 쪽 5 개는 도면이 복부 면에서 153 · 150 · 175 … 로 잡았다 — 중심선에서 잡은 이 열차로는 28 ~ 75 mm 어긋난다 (열차를 둘로 나눌지 결정 대기)</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>#   ! dia 25 는 시제품 값이다 — 도면 철근 번호로 다시 확인할 것</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>srebar</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>V-L</t>
+        </is>
+      </c>
+      <c r="C212" t="n">
+        <v>1</v>
+      </c>
+      <c r="D212" t="n">
+        <v>25</v>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>-1697,-4000,90</t>
+        </is>
+      </c>
+      <c r="G212" t="n">
+        <v>22</v>
+      </c>
+      <c r="H212" t="n">
+        <v>150</v>
+      </c>
+      <c r="N212" t="inlineStr">
+        <is>
+          <t>vertical mesh, left half</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>srebar</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>V-R</t>
+        </is>
+      </c>
+      <c r="C213" t="n">
+        <v>1</v>
+      </c>
+      <c r="D213" t="n">
+        <v>25</v>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>1697,-4000,90</t>
+        </is>
+      </c>
+      <c r="G213" t="n">
+        <v>22</v>
+      </c>
+      <c r="H213" t="n">
+        <v>150</v>
+      </c>
+      <c r="N213" t="inlineStr">
+        <is>
+          <t>vertical mesh, right half</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
         <is>
           <t>end</t>
         </is>

--- a/PSCBOX_BUKSIL_DIAPHRAGM_P1.xlsx
+++ b/PSCBOX_BUKSIL_DIAPHRAGM_P1.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N214"/>
+  <dimension ref="A1:N216"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3142,7 +3142,6 @@
         </is>
       </c>
     </row>
-    <row r="135"/>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
@@ -3428,7 +3427,6 @@
         </is>
       </c>
     </row>
-    <row r="149"/>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
@@ -3726,7 +3724,6 @@
         </is>
       </c>
     </row>
-    <row r="189"/>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
@@ -3856,28 +3853,28 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>#   자리 : 중심선에서 ±(122 + 150k), k = 0…21 (도면의 가운데 122 · 10@150) → 한쪽 22 개, init x = ∓(122 + 150 × 10.5) = ∓1,697</t>
+          <t>#   자리 (도면 치수 153 · 150 · 175 · 3@150 · 118 · 150 · 132 · 190 · 150 · 210 · 10@150 · 122 = 3,500 을 열차 둘로) — 한쪽 22 개 = 11 + 11</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>#   ① 외곽만 본 철근을 덕트가 제 칸(±75) 안에서 옆으로 민다  ② 밀린 자리에서 개구부가 자른다 (위 · 아래 두 토막)</t>
+          <t>#     V   가운데 : 중심선에서 122 + 150k (k 0…10)            → 한가운데 x = ∓(122 + 150 × 5) = ∓872</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>#   ! 복부 쪽 5 개는 도면이 복부 면에서 153 · 150 · 175 … 로 잡았다 — 중심선에서 잡은 이 열차로는 28 ~ 75 mm 어긋난다 (열차를 둘로 나눌지 결정 대기)</t>
+          <t>#     VW  복부   : 복부 바깥면(∓3,500)에서 153 + 150k (k 0…10) → 한가운데 x = ∓(3,500 − 153 − 750) = ∓2,597   (사용자 결정 (가) 2026-10-18)</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>#   ! dia 25 는 시제품 값이다 — 도면 철근 번호로 다시 확인할 것</t>
+          <t>#   덕트가 먼저 제 칸(±75) 안에서 옆으로 밀고, 그 자리에서 개구부가 자른다. ! dia 25 는 시제품 값 — 도면 철근 번호로 다시 확인할 것</t>
         </is>
       </c>
     </row>
@@ -3900,18 +3897,18 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>-1697,-4000,90</t>
+          <t>-872,-4000,90</t>
         </is>
       </c>
       <c r="G212" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="H212" t="n">
         <v>150</v>
       </c>
       <c r="N212" t="inlineStr">
         <is>
-          <t>vertical mesh, left half</t>
+          <t>vertical mesh, left  — from the centreline</t>
         </is>
       </c>
     </row>
@@ -3934,23 +3931,91 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>1697,-4000,90</t>
+          <t>872,-4000,90</t>
         </is>
       </c>
       <c r="G213" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="H213" t="n">
         <v>150</v>
       </c>
       <c r="N213" t="inlineStr">
         <is>
-          <t>vertical mesh, right half</t>
+          <t>vertical mesh, right — from the centreline</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
+        <is>
+          <t>srebar</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>VW-L</t>
+        </is>
+      </c>
+      <c r="C214" t="n">
+        <v>1</v>
+      </c>
+      <c r="D214" t="n">
+        <v>25</v>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>-2597,-4000,90</t>
+        </is>
+      </c>
+      <c r="G214" t="n">
+        <v>11</v>
+      </c>
+      <c r="H214" t="n">
+        <v>150</v>
+      </c>
+      <c r="N214" t="inlineStr">
+        <is>
+          <t>vertical mesh, left  — from the web outer face (153 + 150k)</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>srebar</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>VW-R</t>
+        </is>
+      </c>
+      <c r="C215" t="n">
+        <v>1</v>
+      </c>
+      <c r="D215" t="n">
+        <v>25</v>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>2597,-4000,90</t>
+        </is>
+      </c>
+      <c r="G215" t="n">
+        <v>11</v>
+      </c>
+      <c r="H215" t="n">
+        <v>150</v>
+      </c>
+      <c r="N215" t="inlineStr">
+        <is>
+          <t>vertical mesh, right — from the web outer face (153 + 150k)</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
         <is>
           <t>end</t>
         </is>

--- a/PSCBOX_BUKSIL_DIAPHRAGM_P1.xlsx
+++ b/PSCBOX_BUKSIL_DIAPHRAGM_P1.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N216"/>
+  <dimension ref="A1:N227"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3818,7 +3818,7 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>#   도면 치수 (가로 철근 y, 위에서) : 97.5 · 26@150 = 3,900 · 113 · 187 · 18@150 = 2,700 · 125 · 77.5</t>
+          <t>#   도면 치수 (가로 철근 깊이, 중심선에서 위부터) : 97.5 · 30@150 = 4,500 · 113 · 187 · 18@150 = 2,700 · 125 · 77.5 = 7,800   (2026-10-18 벡터로 다시 잼 — 처음 적은 26@150 은 틀렸다)</t>
         </is>
       </c>
     </row>
@@ -4016,6 +4016,191 @@
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t># ---- srebar code 1 : 가로 면 철근망 (2026-10-18) — 데크와 나란 (−3 %, rot = atan(−0.03) = −1.7184°) ----</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>#   rot −1.7184 의 열차는 철근에 수직으로 **아래로** 행진한다. init y 는 중심선(x 0)의 깊이 — 도면 벡터 52 개(자홍 · 분홍 선 쌍)의 중심</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>#     H-T  위에서 98 + 150k (k 0…30, 31 개)  한가운데 2,348      H-M  4,710.5 하나 (위 열차 끝에서 112.5)</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>#     H-B  4,897.5 + 150k (k 0…18, 19 개)  한가운데 6,247.5    H-S  7,722.5 하나 (밑면에서 77.5)</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>#   ! 위 4 개(깊이 98 · 247.5 · 397.5 · 547.5)가 **캔틸레버로 나간다** (끝 x ±6,148 · ±5,167 · ±4,316 · ±3,495) — 도면은 52 개 전부 복부 면(±3,428)에서 멈춘다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>#     2D 단면에서는 캔틸레버도 이어진 콘크리트라 철근이 거기까지 자란다. 격벽의 범위를 어떻게 줄지 결정 대기.</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>srebar</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>H-T</t>
+        </is>
+      </c>
+      <c r="C223" t="n">
+        <v>1</v>
+      </c>
+      <c r="D223" t="n">
+        <v>25</v>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>0,-2348,-1.7184</t>
+        </is>
+      </c>
+      <c r="G223" t="n">
+        <v>31</v>
+      </c>
+      <c r="H223" t="n">
+        <v>150</v>
+      </c>
+      <c r="N223" t="inlineStr">
+        <is>
+          <t>horizontal mesh, from the deck (98 + 150k)</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>srebar</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>H-M</t>
+        </is>
+      </c>
+      <c r="C224" t="n">
+        <v>1</v>
+      </c>
+      <c r="D224" t="n">
+        <v>25</v>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>0,-4710.5,-1.7184</t>
+        </is>
+      </c>
+      <c r="G224" t="n">
+        <v>1</v>
+      </c>
+      <c r="H224" t="n">
+        <v>150</v>
+      </c>
+      <c r="N224" t="inlineStr">
+        <is>
+          <t>horizontal mesh, single bar between the two trains</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>srebar</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>H-B</t>
+        </is>
+      </c>
+      <c r="C225" t="n">
+        <v>1</v>
+      </c>
+      <c r="D225" t="n">
+        <v>25</v>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>0,-6247.5,-1.7184</t>
+        </is>
+      </c>
+      <c r="G225" t="n">
+        <v>19</v>
+      </c>
+      <c r="H225" t="n">
+        <v>150</v>
+      </c>
+      <c r="N225" t="inlineStr">
+        <is>
+          <t>horizontal mesh, around the opening (cut by it)</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>srebar</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>H-S</t>
+        </is>
+      </c>
+      <c r="C226" t="n">
+        <v>1</v>
+      </c>
+      <c r="D226" t="n">
+        <v>25</v>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>0,-7722.5,-1.7184</t>
+        </is>
+      </c>
+      <c r="G226" t="n">
+        <v>1</v>
+      </c>
+      <c r="H226" t="n">
+        <v>150</v>
+      </c>
+      <c r="N226" t="inlineStr">
+        <is>
+          <t>horizontal mesh, 77.5 above the soffit</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
         <is>
           <t>end</t>
         </is>

--- a/PSCBOX_BUKSIL_DIAPHRAGM_P1.xlsx
+++ b/PSCBOX_BUKSIL_DIAPHRAGM_P1.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N227"/>
+  <dimension ref="A1:N219"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3797,14 +3797,14 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>#   면 철근망 : 세로(⑩ ⑪ 고리의 세로 다리 · ⑬) · 가로(⑫ ⑭) 대부분 150 간격 — 자리에서 태어나 양쪽으로 자라다</t>
+          <t>#   면 철근망 : 세로는 ⑩ 고리의 세로 다리(crebar) · 가로(⑫ ⑭) 는 srebar code 1 — 대부분 150 간격</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>#     처음 만나는 피복선(외곽 · 개구부 · 덕트)에서 멈춘다. 개구부에서 저절로 잘린다.</t>
+          <t>#     덕트 · 매입물은 미는 장(옆으로 민다), 개구부는 자르는 장(토막낸다). 미는 것이 먼저다.</t>
         </is>
       </c>
     </row>
@@ -3832,151 +3832,70 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t># ---- srebar code 1 : 세로 면 철근망 — 덕트가 먼저 밀고, 개구부가 나중에 자른다 (2026-10-18) ----</t>
+          <t># ---- 세로 철근 = 폐합철근 ⑩ 의 세로 다리 (위 crebar 행) — 따로 철근망을 넣지 않는다 (2026-10-18 사용자) ----</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t># srebar | id | code | dia | init x,y,rot | range | num | ctc | | | | | z</t>
+          <t>#   세로 철근망 V · VW 를 넣었다가 지웠다 — ⑩ 과 같은 자리에 두 번 서 있었다. 이제 ⑩ 이 덕트에 밀리고(제 칸 ±ctc/2) 그 자리에서 개구부에 잘린다.</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>#   rot 90 = 세로 철근. 열차는 +x 로 행진하고 init 이 열차의 한가운데다. 철근 길이는 입력이 아니다 — 그 직선 위의 콘크리트가 낸다.</t>
+          <t>#   ! ⑩ 의 자리(cell · 150 균등 → −3,000 ~ 3,000 · 41 자리)는 도면(중심선에서 122 + 150k · 복부 바깥면에서 153 + 150k · 한쪽 22)과 다르다 — 결정 대기</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>#   자리 (도면 치수 153 · 150 · 175 · 3@150 · 118 · 150 · 132 · 190 · 150 · 210 · 10@150 · 122 = 3,500 을 열차 둘로) — 한쪽 22 개 = 11 + 11</t>
+          <t>#</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>#     V   가운데 : 중심선에서 122 + 150k (k 0…10)            → 한가운데 x = ∓(122 + 150 × 5) = ∓872</t>
+          <t># ---- srebar code 1 : 가로 면 철근망 (2026-10-18) — 데크와 나란 (−3 %, rot = atan(−0.03) = −1.7184°) ----</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>#     VW  복부   : 복부 바깥면(∓3,500)에서 153 + 150k (k 0…10) → 한가운데 x = ∓(3,500 − 153 − 750) = ∓2,597   (사용자 결정 (가) 2026-10-18)</t>
+          <t>#   rot −1.7184 의 열차는 철근에 수직으로 **아래로** 행진한다. init y 는 중심선(x 0)의 깊이 — 도면 벡터 52 개(자홍 · 분홍 선 쌍)의 중심</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>#   덕트가 먼저 제 칸(±75) 안에서 옆으로 밀고, 그 자리에서 개구부가 자른다. ! dia 25 는 시제품 값 — 도면 철근 번호로 다시 확인할 것</t>
+          <t>#     H-T  위에서 98 + 150k (k 0…30, 31 개)  한가운데 2,348      H-M  4,710.5 하나 (위 열차 끝에서 112.5)</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>srebar</t>
-        </is>
-      </c>
-      <c r="B212" t="inlineStr">
-        <is>
-          <t>V-L</t>
-        </is>
-      </c>
-      <c r="C212" t="n">
-        <v>1</v>
-      </c>
-      <c r="D212" t="n">
-        <v>25</v>
-      </c>
-      <c r="E212" t="inlineStr">
-        <is>
-          <t>-872,-4000,90</t>
-        </is>
-      </c>
-      <c r="G212" t="n">
-        <v>11</v>
-      </c>
-      <c r="H212" t="n">
-        <v>150</v>
-      </c>
-      <c r="N212" t="inlineStr">
-        <is>
-          <t>vertical mesh, left  — from the centreline</t>
+          <t>#     H-B  4,897.5 + 150k (k 0…18, 19 개)  한가운데 6,247.5    H-S  7,722.5 하나 (밑면에서 77.5)</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>srebar</t>
-        </is>
-      </c>
-      <c r="B213" t="inlineStr">
-        <is>
-          <t>V-R</t>
-        </is>
-      </c>
-      <c r="C213" t="n">
-        <v>1</v>
-      </c>
-      <c r="D213" t="n">
-        <v>25</v>
-      </c>
-      <c r="E213" t="inlineStr">
-        <is>
-          <t>872,-4000,90</t>
-        </is>
-      </c>
-      <c r="G213" t="n">
-        <v>11</v>
-      </c>
-      <c r="H213" t="n">
-        <v>150</v>
-      </c>
-      <c r="N213" t="inlineStr">
-        <is>
-          <t>vertical mesh, right — from the centreline</t>
+          <t>#   ! 위 4 개(깊이 98 · 247.5 · 397.5 · 547.5)가 **캔틸레버로 나간다** (끝 x ±6,148 · ±5,167 · ±4,316 · ±3,495) — 도면은 52 개 전부 복부 면(±3,428)에서 멈춘다.</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>srebar</t>
-        </is>
-      </c>
-      <c r="B214" t="inlineStr">
-        <is>
-          <t>VW-L</t>
-        </is>
-      </c>
-      <c r="C214" t="n">
-        <v>1</v>
-      </c>
-      <c r="D214" t="n">
-        <v>25</v>
-      </c>
-      <c r="E214" t="inlineStr">
-        <is>
-          <t>-2597,-4000,90</t>
-        </is>
-      </c>
-      <c r="G214" t="n">
-        <v>11</v>
-      </c>
-      <c r="H214" t="n">
-        <v>150</v>
-      </c>
-      <c r="N214" t="inlineStr">
-        <is>
-          <t>vertical mesh, left  — from the web outer face (153 + 150k)</t>
+          <t>#     2D 단면에서는 캔틸레버도 이어진 콘크리트라 철근이 거기까지 자란다. 격벽의 범위를 어떻게 줄지 결정 대기.</t>
         </is>
       </c>
     </row>
@@ -3988,7 +3907,7 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>VW-R</t>
+          <t>H-T</t>
         </is>
       </c>
       <c r="C215" t="n">
@@ -3999,208 +3918,125 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>2597,-4000,90</t>
+          <t>0,-2348,-1.7184</t>
         </is>
       </c>
       <c r="G215" t="n">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="H215" t="n">
         <v>150</v>
       </c>
       <c r="N215" t="inlineStr">
         <is>
-          <t>vertical mesh, right — from the web outer face (153 + 150k)</t>
+          <t>horizontal mesh, from the deck (98 + 150k)</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>srebar</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>H-M</t>
+        </is>
+      </c>
+      <c r="C216" t="n">
+        <v>1</v>
+      </c>
+      <c r="D216" t="n">
+        <v>25</v>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>0,-4710.5,-1.7184</t>
+        </is>
+      </c>
+      <c r="G216" t="n">
+        <v>1</v>
+      </c>
+      <c r="H216" t="n">
+        <v>150</v>
+      </c>
+      <c r="N216" t="inlineStr">
+        <is>
+          <t>horizontal mesh, single bar between the two trains</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t># ---- srebar code 1 : 가로 면 철근망 (2026-10-18) — 데크와 나란 (−3 %, rot = atan(−0.03) = −1.7184°) ----</t>
+          <t>srebar</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>H-B</t>
+        </is>
+      </c>
+      <c r="C217" t="n">
+        <v>1</v>
+      </c>
+      <c r="D217" t="n">
+        <v>25</v>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>0,-6247.5,-1.7184</t>
+        </is>
+      </c>
+      <c r="G217" t="n">
+        <v>19</v>
+      </c>
+      <c r="H217" t="n">
+        <v>150</v>
+      </c>
+      <c r="N217" t="inlineStr">
+        <is>
+          <t>horizontal mesh, around the opening (cut by it)</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>#   rot −1.7184 의 열차는 철근에 수직으로 **아래로** 행진한다. init y 는 중심선(x 0)의 깊이 — 도면 벡터 52 개(자홍 · 분홍 선 쌍)의 중심</t>
+          <t>srebar</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>H-S</t>
+        </is>
+      </c>
+      <c r="C218" t="n">
+        <v>1</v>
+      </c>
+      <c r="D218" t="n">
+        <v>25</v>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>0,-7722.5,-1.7184</t>
+        </is>
+      </c>
+      <c r="G218" t="n">
+        <v>1</v>
+      </c>
+      <c r="H218" t="n">
+        <v>150</v>
+      </c>
+      <c r="N218" t="inlineStr">
+        <is>
+          <t>horizontal mesh, 77.5 above the soffit</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
-        <is>
-          <t>#     H-T  위에서 98 + 150k (k 0…30, 31 개)  한가운데 2,348      H-M  4,710.5 하나 (위 열차 끝에서 112.5)</t>
-        </is>
-      </c>
-    </row>
-    <row r="220">
-      <c r="A220" t="inlineStr">
-        <is>
-          <t>#     H-B  4,897.5 + 150k (k 0…18, 19 개)  한가운데 6,247.5    H-S  7,722.5 하나 (밑면에서 77.5)</t>
-        </is>
-      </c>
-    </row>
-    <row r="221">
-      <c r="A221" t="inlineStr">
-        <is>
-          <t>#   ! 위 4 개(깊이 98 · 247.5 · 397.5 · 547.5)가 **캔틸레버로 나간다** (끝 x ±6,148 · ±5,167 · ±4,316 · ±3,495) — 도면은 52 개 전부 복부 면(±3,428)에서 멈춘다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="222">
-      <c r="A222" t="inlineStr">
-        <is>
-          <t>#     2D 단면에서는 캔틸레버도 이어진 콘크리트라 철근이 거기까지 자란다. 격벽의 범위를 어떻게 줄지 결정 대기.</t>
-        </is>
-      </c>
-    </row>
-    <row r="223">
-      <c r="A223" t="inlineStr">
-        <is>
-          <t>srebar</t>
-        </is>
-      </c>
-      <c r="B223" t="inlineStr">
-        <is>
-          <t>H-T</t>
-        </is>
-      </c>
-      <c r="C223" t="n">
-        <v>1</v>
-      </c>
-      <c r="D223" t="n">
-        <v>25</v>
-      </c>
-      <c r="E223" t="inlineStr">
-        <is>
-          <t>0,-2348,-1.7184</t>
-        </is>
-      </c>
-      <c r="G223" t="n">
-        <v>31</v>
-      </c>
-      <c r="H223" t="n">
-        <v>150</v>
-      </c>
-      <c r="N223" t="inlineStr">
-        <is>
-          <t>horizontal mesh, from the deck (98 + 150k)</t>
-        </is>
-      </c>
-    </row>
-    <row r="224">
-      <c r="A224" t="inlineStr">
-        <is>
-          <t>srebar</t>
-        </is>
-      </c>
-      <c r="B224" t="inlineStr">
-        <is>
-          <t>H-M</t>
-        </is>
-      </c>
-      <c r="C224" t="n">
-        <v>1</v>
-      </c>
-      <c r="D224" t="n">
-        <v>25</v>
-      </c>
-      <c r="E224" t="inlineStr">
-        <is>
-          <t>0,-4710.5,-1.7184</t>
-        </is>
-      </c>
-      <c r="G224" t="n">
-        <v>1</v>
-      </c>
-      <c r="H224" t="n">
-        <v>150</v>
-      </c>
-      <c r="N224" t="inlineStr">
-        <is>
-          <t>horizontal mesh, single bar between the two trains</t>
-        </is>
-      </c>
-    </row>
-    <row r="225">
-      <c r="A225" t="inlineStr">
-        <is>
-          <t>srebar</t>
-        </is>
-      </c>
-      <c r="B225" t="inlineStr">
-        <is>
-          <t>H-B</t>
-        </is>
-      </c>
-      <c r="C225" t="n">
-        <v>1</v>
-      </c>
-      <c r="D225" t="n">
-        <v>25</v>
-      </c>
-      <c r="E225" t="inlineStr">
-        <is>
-          <t>0,-6247.5,-1.7184</t>
-        </is>
-      </c>
-      <c r="G225" t="n">
-        <v>19</v>
-      </c>
-      <c r="H225" t="n">
-        <v>150</v>
-      </c>
-      <c r="N225" t="inlineStr">
-        <is>
-          <t>horizontal mesh, around the opening (cut by it)</t>
-        </is>
-      </c>
-    </row>
-    <row r="226">
-      <c r="A226" t="inlineStr">
-        <is>
-          <t>srebar</t>
-        </is>
-      </c>
-      <c r="B226" t="inlineStr">
-        <is>
-          <t>H-S</t>
-        </is>
-      </c>
-      <c r="C226" t="n">
-        <v>1</v>
-      </c>
-      <c r="D226" t="n">
-        <v>25</v>
-      </c>
-      <c r="E226" t="inlineStr">
-        <is>
-          <t>0,-7722.5,-1.7184</t>
-        </is>
-      </c>
-      <c r="G226" t="n">
-        <v>1</v>
-      </c>
-      <c r="H226" t="n">
-        <v>150</v>
-      </c>
-      <c r="N226" t="inlineStr">
-        <is>
-          <t>horizontal mesh, 77.5 above the soffit</t>
-        </is>
-      </c>
-    </row>
-    <row r="227">
-      <c r="A227" t="inlineStr">
         <is>
           <t>end</t>
         </is>

--- a/PSCBOX_BUKSIL_DIAPHRAGM_P1.xlsx
+++ b/PSCBOX_BUKSIL_DIAPHRAGM_P1.xlsx
@@ -3846,7 +3846,7 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>#   ! ⑩ 의 자리(cell · 150 균등 → −3,000 ~ 3,000 · 41 자리)는 도면(중심선에서 122 + 150k · 복부 바깥면에서 153 + 150k · 한쪽 22)과 다르다 — 결정 대기</t>
+          <t>#   ⑩ 의 자리는 cell · 150 균등 (−3,000 ~ 3,000 · 41 자리) 그대로 둔다 — 복부 쪽(도면 ±3,347 까지)에 세로 철근이 없는 채로 (2026-10-18 사용자 결정). 비교표에는 차이로 적는다</t>
         </is>
       </c>
     </row>

--- a/PSCBOX_BUKSIL_DIAPHRAGM_P1.xlsx
+++ b/PSCBOX_BUKSIL_DIAPHRAGM_P1.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N219"/>
+  <dimension ref="A1:N236"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3727,7 +3727,7 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t># ---- 다음에 넣을 것 : 가로 철근망 · 개구부 보강 (srebar code 1) — 세로 철근망은 맨 아래에 넣었다 ----</t>
+          <t># ---- 도면 메모 (8-244) : 면 철근 · 개구부 보강 — 철근 행은 맨 아래에 있다 ----</t>
         </is>
       </c>
     </row>
@@ -4037,6 +4037,365 @@
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t># ---- srebar code 1 : 개구부 보강 M1 · M2 · M3 (2026-10-18) — 길이 고정 (8 번 칸 len) ----</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t># srebar | id | code | dia | init x,y,rot | range | num | ctc | len | | | | z</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>#   len 을 적으면 길이가 고정이다 — 자리를 한가운데로 ±len/2. 외곽 피복이 줄이지 않고, 덕트가 밀고 개구부가 자르는 것은 철근망과 같다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>#   자리는 8-244 녹색 선 33 개(외곽선 쌍은 한 철근으로)에서 잼 — init 은 가운데 철근의 중점, 열차 간격은 도면 99 ~ 101.6 → 100.</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>#     M1 H25 L 2,000 세로 : x ∓924 · ∓825 · ∓726 (왼쪽) / 725 · 824 · 925 (오른쪽) · 첫 줄이 개구부 옆면에서 126</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>#     M2 H25 L 2,000 가로 (−3 %) : 위 −4,487 · −4,587 · −4,687 / 아래 −6,424 · −6,525 · −6,624 (중심선 깊이)</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>#     M3 H25 L 1,500 사선 : 모서리 접기 넷에 셋씩 · 도면 각 44.15° / 134.15°</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>#   ! 자리를 도면에서 가져왔으므로 도면과 맞는 것은 검증이 아니다 (중점 2.2 mm 안 · 길이 2 mm 안)</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>srebar</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>M1-L</t>
+        </is>
+      </c>
+      <c r="C228" t="n">
+        <v>1</v>
+      </c>
+      <c r="D228" t="n">
+        <v>25</v>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>-824.7,-5556,90</t>
+        </is>
+      </c>
+      <c r="G228" t="n">
+        <v>3</v>
+      </c>
+      <c r="H228" t="n">
+        <v>100</v>
+      </c>
+      <c r="I228" t="n">
+        <v>2000</v>
+      </c>
+      <c r="N228" t="inlineStr">
+        <is>
+          <t>opening bar M1, vertical, left of the opening</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>srebar</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>M1-R</t>
+        </is>
+      </c>
+      <c r="C229" t="n">
+        <v>1</v>
+      </c>
+      <c r="D229" t="n">
+        <v>25</v>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>823.6,-5567.4,90</t>
+        </is>
+      </c>
+      <c r="G229" t="n">
+        <v>3</v>
+      </c>
+      <c r="H229" t="n">
+        <v>100</v>
+      </c>
+      <c r="I229" t="n">
+        <v>2000</v>
+      </c>
+      <c r="N229" t="inlineStr">
+        <is>
+          <t>opening bar M1, vertical, right</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>srebar</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>M2-T</t>
+        </is>
+      </c>
+      <c r="C230" t="n">
+        <v>1</v>
+      </c>
+      <c r="D230" t="n">
+        <v>25</v>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>7.1,-4587,-1.7184</t>
+        </is>
+      </c>
+      <c r="G230" t="n">
+        <v>3</v>
+      </c>
+      <c r="H230" t="n">
+        <v>100</v>
+      </c>
+      <c r="I230" t="n">
+        <v>2000</v>
+      </c>
+      <c r="N230" t="inlineStr">
+        <is>
+          <t>opening bar M2, above the opening (parallel to the -3% faces)</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>srebar</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>M2-B</t>
+        </is>
+      </c>
+      <c r="C231" t="n">
+        <v>1</v>
+      </c>
+      <c r="D231" t="n">
+        <v>25</v>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>-5.7,-6524.9,-1.7184</t>
+        </is>
+      </c>
+      <c r="G231" t="n">
+        <v>3</v>
+      </c>
+      <c r="H231" t="n">
+        <v>100</v>
+      </c>
+      <c r="I231" t="n">
+        <v>2000</v>
+      </c>
+      <c r="N231" t="inlineStr">
+        <is>
+          <t>opening bar M2, below the opening</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>srebar</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>M3-UL</t>
+        </is>
+      </c>
+      <c r="C232" t="n">
+        <v>1</v>
+      </c>
+      <c r="D232" t="n">
+        <v>25</v>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>-614,-4766.1,44.15</t>
+        </is>
+      </c>
+      <c r="G232" t="n">
+        <v>3</v>
+      </c>
+      <c r="H232" t="n">
+        <v>100</v>
+      </c>
+      <c r="I232" t="n">
+        <v>1500</v>
+      </c>
+      <c r="N232" t="inlineStr">
+        <is>
+          <t>opening bar M3, diagonal, upper-left chamfer</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>srebar</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>M3-UR</t>
+        </is>
+      </c>
+      <c r="C233" t="n">
+        <v>1</v>
+      </c>
+      <c r="D233" t="n">
+        <v>25</v>
+      </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>636.9,-4782.6,134.15</t>
+        </is>
+      </c>
+      <c r="G233" t="n">
+        <v>3</v>
+      </c>
+      <c r="H233" t="n">
+        <v>100</v>
+      </c>
+      <c r="I233" t="n">
+        <v>1500</v>
+      </c>
+      <c r="N233" t="inlineStr">
+        <is>
+          <t>opening bar M3, diagonal, upper-right chamfer</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>srebar</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>M3-LL</t>
+        </is>
+      </c>
+      <c r="C234" t="n">
+        <v>1</v>
+      </c>
+      <c r="D234" t="n">
+        <v>25</v>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>-627.3,-6307.7,134.15</t>
+        </is>
+      </c>
+      <c r="G234" t="n">
+        <v>3</v>
+      </c>
+      <c r="H234" t="n">
+        <v>100</v>
+      </c>
+      <c r="I234" t="n">
+        <v>1500</v>
+      </c>
+      <c r="N234" t="inlineStr">
+        <is>
+          <t>opening bar M3, diagonal, lower-left chamfer</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>srebar</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>M3-LR</t>
+        </is>
+      </c>
+      <c r="C235" t="n">
+        <v>1</v>
+      </c>
+      <c r="D235" t="n">
+        <v>25</v>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>622.3,-6342,44.15</t>
+        </is>
+      </c>
+      <c r="G235" t="n">
+        <v>3</v>
+      </c>
+      <c r="H235" t="n">
+        <v>100</v>
+      </c>
+      <c r="I235" t="n">
+        <v>1500</v>
+      </c>
+      <c r="N235" t="inlineStr">
+        <is>
+          <t>opening bar M3, diagonal, lower-right chamfer</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
         <is>
           <t>end</t>
         </is>

--- a/PSCBOX_BUKSIL_DIAPHRAGM_P1.xlsx
+++ b/PSCBOX_BUKSIL_DIAPHRAGM_P1.xlsx
@@ -3142,6 +3142,7 @@
         </is>
       </c>
     </row>
+    <row r="135"/>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
@@ -3427,6 +3428,7 @@
         </is>
       </c>
     </row>
+    <row r="149"/>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
@@ -3724,6 +3726,7 @@
         </is>
       </c>
     </row>
+    <row r="189"/>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
@@ -4045,14 +4048,14 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t># ---- srebar code 1 : 개구부 보강 M1 · M2 · M3 (2026-10-18) — 길이 고정 (8 번 칸 len) ----</t>
+          <t># ---- srebar code 1 : 개구부 보강 M1 · M2 · M3 (2026-10-18) — 길이 고정(8 번 칸 len) · 개구부 면으로 끌려가 J 최소에 앉는다(9 번 칸 seat open) ----</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t># srebar | id | code | dia | init x,y,rot | range | num | ctc | len | | | | z</t>
+          <t># srebar | id | code | dia | init x,y,rot | range | num | ctc | len | seat | | | z</t>
         </is>
       </c>
     </row>
@@ -4066,7 +4069,7 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>#   자리는 8-244 녹색 선 33 개(외곽선 쌍은 한 철근으로)에서 잼 — init 은 가운데 철근의 중점, 열차 간격은 도면 99 ~ 101.6 → 100.</t>
+          <t>#   init 은 출발점이다 — 8-244 녹색 선 33 개(외곽선 쌍은 한 철근으로)에서 잰 가운데 철근의 중점. 열차는 거기서 나란한 개구부 면 쪽으로 끌려가 피복선(내측 30 + 12.5)에 앉는다.</t>
         </is>
       </c>
     </row>
@@ -4094,7 +4097,7 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>#   ! 자리를 도면에서 가져왔으므로 도면과 맞는 것은 검증이 아니다 (중점 2.2 mm 안 · 길이 2 mm 안)</t>
+          <t>#   ! 도면은 첫 줄을 개구부 면에서 약 100 ~ 126 에 그렸다 — 피복선에 앉은 엔진보다 58 ~ 83 mm 멀다 (결정 대기)</t>
         </is>
       </c>
     </row>
@@ -4129,6 +4132,11 @@
       <c r="I228" t="n">
         <v>2000</v>
       </c>
+      <c r="J228" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
       <c r="N228" t="inlineStr">
         <is>
           <t>opening bar M1, vertical, left of the opening</t>
@@ -4166,6 +4174,11 @@
       <c r="I229" t="n">
         <v>2000</v>
       </c>
+      <c r="J229" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
       <c r="N229" t="inlineStr">
         <is>
           <t>opening bar M1, vertical, right</t>
@@ -4203,6 +4216,11 @@
       <c r="I230" t="n">
         <v>2000</v>
       </c>
+      <c r="J230" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
       <c r="N230" t="inlineStr">
         <is>
           <t>opening bar M2, above the opening (parallel to the -3% faces)</t>
@@ -4240,6 +4258,11 @@
       <c r="I231" t="n">
         <v>2000</v>
       </c>
+      <c r="J231" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
       <c r="N231" t="inlineStr">
         <is>
           <t>opening bar M2, below the opening</t>
@@ -4277,6 +4300,11 @@
       <c r="I232" t="n">
         <v>1500</v>
       </c>
+      <c r="J232" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
       <c r="N232" t="inlineStr">
         <is>
           <t>opening bar M3, diagonal, upper-left chamfer</t>
@@ -4314,6 +4342,11 @@
       <c r="I233" t="n">
         <v>1500</v>
       </c>
+      <c r="J233" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
       <c r="N233" t="inlineStr">
         <is>
           <t>opening bar M3, diagonal, upper-right chamfer</t>
@@ -4351,6 +4384,11 @@
       <c r="I234" t="n">
         <v>1500</v>
       </c>
+      <c r="J234" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
       <c r="N234" t="inlineStr">
         <is>
           <t>opening bar M3, diagonal, lower-left chamfer</t>
@@ -4387,6 +4425,11 @@
       </c>
       <c r="I235" t="n">
         <v>1500</v>
+      </c>
+      <c r="J235" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
       </c>
       <c r="N235" t="inlineStr">
         <is>
